--- a/cet4/result/02_重生校园_琴键上的女神/02_重生校园_琴键上的女神_学习版.xlsx
+++ b/cet4/result/02_重生校园_琴键上的女神/02_重生校园_琴键上的女神_学习版.xlsx
@@ -397,871 +397,745 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D52"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>electronics</v>
       </c>
       <c r="B2" t="str">
-        <v>electronics</v>
+        <v>/ɪˌlekˈtrɑːnɪks/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>电子学</v>
       </c>
-      <c r="D2" t="str">
-        <v>electronics(电子学)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>violin</v>
       </c>
       <c r="B3" t="str">
-        <v>violin</v>
+        <v>/ˌvaɪəˈlɪn/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>小提琴</v>
       </c>
-      <c r="D3" t="str">
-        <v>violin(小提琴)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>birth</v>
       </c>
       <c r="B4" t="str">
-        <v>birth</v>
+        <v>/bɜːrθ/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>出生</v>
       </c>
-      <c r="D4" t="str">
-        <v>birth(出生)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>cafeteria</v>
       </c>
       <c r="B5" t="str">
-        <v>cafeteria</v>
+        <v>/ˌkæfəˈtɪriə/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>自助餐厅</v>
       </c>
-      <c r="D5" t="str">
-        <v>cafeteria(自助餐厅)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>dollar</v>
       </c>
       <c r="B6" t="str">
-        <v>dollar</v>
+        <v>/ˈdɑːlər/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>美元</v>
       </c>
-      <c r="D6" t="str">
-        <v>dollar(美元)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>learn</v>
       </c>
       <c r="B7" t="str">
-        <v>learn</v>
+        <v>/lɜːrn/</v>
       </c>
       <c r="C7" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D7" t="str">
         <v>学习</v>
       </c>
-      <c r="D7" t="str">
-        <v>learn(学习)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>anxiety</v>
       </c>
       <c r="B8" t="str">
-        <v>anxiety</v>
+        <v>/æŋˈzaɪəti/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>焦虑</v>
       </c>
-      <c r="D8" t="str">
-        <v>anxiety(焦虑)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>heading</v>
       </c>
       <c r="B9" t="str">
-        <v>heading</v>
+        <v>/ˈhedɪŋ/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>标题</v>
       </c>
-      <c r="D9" t="str">
-        <v>heading(标题)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>solve</v>
       </c>
       <c r="B10" t="str">
-        <v>dollar</v>
+        <v>/sɑːlv/</v>
       </c>
       <c r="C10" t="str">
-        <v>美元</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D10" t="str">
-        <v>dollar(美元)📢</v>
+        <v>解决</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>shortage</v>
       </c>
       <c r="B11" t="str">
-        <v>solve</v>
+        <v>/ˈʃɔːrtɪdʒ/</v>
       </c>
       <c r="C11" t="str">
-        <v>解决</v>
+        <v>n.</v>
       </c>
       <c r="D11" t="str">
-        <v>solve(解决)📢</v>
+        <v>短缺</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>formula</v>
       </c>
       <c r="B12" t="str">
-        <v>shortage</v>
+        <v>/ˈfɔːrmjələ/</v>
       </c>
       <c r="C12" t="str">
-        <v>短缺</v>
+        <v>n.</v>
       </c>
       <c r="D12" t="str">
-        <v>shortage(短缺)📢</v>
+        <v>公式</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>freely</v>
       </c>
       <c r="B13" t="str">
-        <v>formula</v>
+        <v>/ˈfriːli/</v>
       </c>
       <c r="C13" t="str">
-        <v>公式</v>
+        <v>v./adv.</v>
       </c>
       <c r="D13" t="str">
-        <v>formula(公式)📢</v>
+        <v>自由地</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>robe</v>
       </c>
       <c r="B14" t="str">
-        <v>freely</v>
+        <v>/roʊb/</v>
       </c>
       <c r="C14" t="str">
-        <v>自由地</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D14" t="str">
-        <v>freely(自由地)📢</v>
+        <v>长袍</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>completely</v>
       </c>
       <c r="B15" t="str">
-        <v>robe</v>
+        <v>/kəmˈpliːtli/</v>
       </c>
       <c r="C15" t="str">
-        <v>长袍</v>
+        <v>v./adv.</v>
       </c>
       <c r="D15" t="str">
-        <v>robe(长袍)📢</v>
+        <v>完全地</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>gravity</v>
       </c>
       <c r="B16" t="str">
-        <v>learn</v>
+        <v>/ˈɡrævəti/</v>
       </c>
       <c r="C16" t="str">
-        <v>学习</v>
+        <v>n.</v>
       </c>
       <c r="D16" t="str">
-        <v>learn(学习)📢</v>
+        <v>重力</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>noise</v>
       </c>
       <c r="B17" t="str">
-        <v>completely</v>
+        <v>/nɔɪz/</v>
       </c>
       <c r="C17" t="str">
-        <v>完全地</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D17" t="str">
-        <v>completely(完全地)📢</v>
+        <v>噪音</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>calm</v>
       </c>
       <c r="B18" t="str">
-        <v>gravity</v>
+        <v>/kɑːm/</v>
       </c>
       <c r="C18" t="str">
-        <v>重力</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D18" t="str">
-        <v>gravity(重力)📢</v>
+        <v>平静</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>contrary</v>
       </c>
       <c r="B19" t="str">
-        <v>noise</v>
+        <v>/'kɑntreri/</v>
       </c>
       <c r="C19" t="str">
-        <v>噪音</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D19" t="str">
-        <v>noise(噪音)📢</v>
+        <v>相反的</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>prefer</v>
       </c>
       <c r="B20" t="str">
-        <v>calm</v>
+        <v>/prɪˈfɜːr/</v>
       </c>
       <c r="C20" t="str">
-        <v>平静</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D20" t="str">
-        <v>calm(平静)📢</v>
+        <v>更喜欢</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>temper</v>
       </c>
       <c r="B21" t="str">
-        <v>contrary</v>
+        <v>/ˈtempər/</v>
       </c>
       <c r="C21" t="str">
-        <v>相反的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D21" t="str">
-        <v>contrary(相反的)📢</v>
+        <v>脾气</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>sack</v>
       </c>
       <c r="B22" t="str">
-        <v>prefer</v>
+        <v>/sæk/</v>
       </c>
       <c r="C22" t="str">
-        <v>更喜欢</v>
+        <v>n./vt.</v>
       </c>
       <c r="D22" t="str">
-        <v>prefer(更喜欢)📢</v>
+        <v>解雇</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>blade</v>
       </c>
       <c r="B23" t="str">
-        <v>temper</v>
+        <v>/bleɪd/</v>
       </c>
       <c r="C23" t="str">
-        <v>脾气</v>
+        <v>n.</v>
       </c>
       <c r="D23" t="str">
-        <v>temper(脾气)📢</v>
+        <v>刀片</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>loss</v>
       </c>
       <c r="B24" t="str">
-        <v>sack</v>
+        <v>/lɔːs/</v>
       </c>
       <c r="C24" t="str">
-        <v>解雇</v>
+        <v>n.</v>
       </c>
       <c r="D24" t="str">
-        <v>sack(解雇)📢</v>
+        <v>损失</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>repair</v>
       </c>
       <c r="B25" t="str">
-        <v>blade</v>
+        <v>/rɪˈper/</v>
       </c>
       <c r="C25" t="str">
-        <v>刀片</v>
+        <v>n./v.</v>
       </c>
       <c r="D25" t="str">
-        <v>blade(刀片)📢</v>
+        <v>修理</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>light</v>
       </c>
       <c r="B26" t="str">
-        <v>dollar</v>
+        <v>/laɪt/</v>
       </c>
       <c r="C26" t="str">
-        <v>美元</v>
+        <v>n./vt./vi./v./adj./adv.</v>
       </c>
       <c r="D26" t="str">
-        <v>dollar(美元)📢</v>
+        <v>灯光</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>guard</v>
       </c>
       <c r="B27" t="str">
-        <v>loss</v>
+        <v>/ɡɑːrd/</v>
       </c>
       <c r="C27" t="str">
-        <v>损失</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D27" t="str">
-        <v>loss(损失)📢</v>
+        <v>守卫</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>cycle</v>
       </c>
       <c r="B28" t="str">
-        <v>repair</v>
+        <v>/ˈsaɪkl/</v>
       </c>
       <c r="C28" t="str">
-        <v>修理</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D28" t="str">
-        <v>repair(修理)📢</v>
+        <v>循环</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>green</v>
       </c>
       <c r="B29" t="str">
-        <v>light</v>
+        <v>/ɡriːn/</v>
       </c>
       <c r="C29" t="str">
-        <v>灯光</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D29" t="str">
-        <v>light(灯光)📢</v>
+        <v>绿色</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>madam</v>
       </c>
       <c r="B30" t="str">
-        <v>guard</v>
+        <v>/ˈmædəm/</v>
       </c>
       <c r="C30" t="str">
-        <v>守卫</v>
+        <v>n.</v>
       </c>
       <c r="D30" t="str">
-        <v>guard(守卫)📢</v>
+        <v>女士</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>proportion</v>
       </c>
       <c r="B31" t="str">
-        <v>cycle</v>
+        <v>/prəˈpɔːrʃn/</v>
       </c>
       <c r="C31" t="str">
-        <v>循环</v>
+        <v>n./vt.</v>
       </c>
       <c r="D31" t="str">
-        <v>cycle(循环)📢</v>
+        <v>比例</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>weather</v>
       </c>
       <c r="B32" t="str">
-        <v>green</v>
+        <v>/ˈweðər/</v>
       </c>
       <c r="C32" t="str">
-        <v>绿色</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D32" t="str">
-        <v>green(绿色)📢</v>
+        <v>天气</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>damage</v>
       </c>
       <c r="B33" t="str">
-        <v>madam</v>
+        <v>/ˈdæmɪdʒ/</v>
       </c>
       <c r="C33" t="str">
-        <v>女士</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>madam(女士)📢</v>
+        <v>损害</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>fireman</v>
       </c>
       <c r="B34" t="str">
-        <v>proportion</v>
+        <v>/ˈfaɪərmən/</v>
       </c>
       <c r="C34" t="str">
-        <v>比例</v>
+        <v>n.</v>
       </c>
       <c r="D34" t="str">
-        <v>proportion(比例)📢</v>
+        <v>消防员</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>collision</v>
       </c>
       <c r="B35" t="str">
-        <v>weather</v>
+        <v>/kəˈlɪʒn/</v>
       </c>
       <c r="C35" t="str">
-        <v>天气</v>
+        <v>n.</v>
       </c>
       <c r="D35" t="str">
-        <v>weather(天气)📢</v>
+        <v>碰撞</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>occur</v>
       </c>
       <c r="B36" t="str">
-        <v>completely</v>
+        <v>/əˈkɜːr/</v>
       </c>
       <c r="C36" t="str">
-        <v>完全地</v>
+        <v>vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>completely(完全地)📢</v>
+        <v>发生</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>detection</v>
       </c>
       <c r="B37" t="str">
-        <v>damage</v>
+        <v>/dɪˈtekʃn/</v>
       </c>
       <c r="C37" t="str">
-        <v>损害</v>
+        <v>n.</v>
       </c>
       <c r="D37" t="str">
-        <v>damage(损害)📢</v>
+        <v>探测</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>thank</v>
       </c>
       <c r="B38" t="str">
-        <v>fireman</v>
+        <v>/θæŋk/</v>
       </c>
       <c r="C38" t="str">
-        <v>消防员</v>
+        <v>n./vt./int.</v>
       </c>
       <c r="D38" t="str">
-        <v>fireman(消防员)📢</v>
+        <v>感谢</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>inherit</v>
       </c>
       <c r="B39" t="str">
-        <v>collision</v>
+        <v>/ɪnˈherɪt/</v>
       </c>
       <c r="C39" t="str">
-        <v>碰撞</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D39" t="str">
-        <v>collision(碰撞)📢</v>
+        <v>继承</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>report</v>
       </c>
       <c r="B40" t="str">
-        <v>occur</v>
+        <v>/rɪˈpɔːrt/</v>
       </c>
       <c r="C40" t="str">
-        <v>发生</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D40" t="str">
-        <v>occur(发生)📢</v>
+        <v>报告</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>fit</v>
       </c>
       <c r="B41" t="str">
-        <v>detection</v>
+        <v>/fɪt/</v>
       </c>
       <c r="C41" t="str">
-        <v>探测</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D41" t="str">
-        <v>detection(探测)📢</v>
+        <v>适合</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>flight</v>
       </c>
       <c r="B42" t="str">
-        <v>dollar</v>
+        <v>/flaɪt/</v>
       </c>
       <c r="C42" t="str">
-        <v>美元</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D42" t="str">
-        <v>dollar(美元)📢</v>
+        <v>航班</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>tumble</v>
       </c>
       <c r="B43" t="str">
-        <v>thank</v>
+        <v>/ˈtʌmbl/</v>
       </c>
       <c r="C43" t="str">
-        <v>感谢</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D43" t="str">
-        <v>thank(感谢)📢</v>
+        <v>摔倒</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>ditch</v>
       </c>
       <c r="B44" t="str">
-        <v>inherit</v>
+        <v>/dɪtʃ/</v>
       </c>
       <c r="C44" t="str">
-        <v>继承</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>inherit(继承)📢</v>
+        <v>沟渠</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>huge</v>
       </c>
       <c r="B45" t="str">
-        <v>report</v>
+        <v>/hjuːdʒ/</v>
       </c>
       <c r="C45" t="str">
-        <v>报告</v>
+        <v>n./adj.</v>
       </c>
       <c r="D45" t="str">
-        <v>report(报告)📢</v>
+        <v>巨大的</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>ending</v>
       </c>
       <c r="B46" t="str">
-        <v>fit</v>
+        <v>/ˈendɪŋ/</v>
       </c>
       <c r="C46" t="str">
-        <v>适合</v>
+        <v>n./v.</v>
       </c>
       <c r="D46" t="str">
-        <v>fit(适合)📢</v>
+        <v>结局</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>seal</v>
       </c>
       <c r="B47" t="str">
-        <v>flight</v>
+        <v>/siːl/</v>
       </c>
       <c r="C47" t="str">
-        <v>航班</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D47" t="str">
-        <v>flight(航班)📢</v>
+        <v>印章</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>intelligence</v>
       </c>
       <c r="B48" t="str">
-        <v>tumble</v>
+        <v>/ɪnˈtelɪdʒəns/</v>
       </c>
       <c r="C48" t="str">
-        <v>摔倒</v>
+        <v>n.</v>
       </c>
       <c r="D48" t="str">
-        <v>tumble(摔倒)📢</v>
+        <v>智力</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>troublesome</v>
       </c>
       <c r="B49" t="str">
-        <v>ditch</v>
+        <v>/ˈtrʌblsəm/</v>
       </c>
       <c r="C49" t="str">
-        <v>沟渠</v>
+        <v>adj.</v>
       </c>
       <c r="D49" t="str">
-        <v>ditch(沟渠)📢</v>
+        <v>麻烦</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>reap</v>
       </c>
       <c r="B50" t="str">
-        <v>huge</v>
+        <v>/riːp/</v>
       </c>
       <c r="C50" t="str">
-        <v>巨大的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D50" t="str">
-        <v>huge(巨大的)📢</v>
+        <v>收获</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>owe</v>
       </c>
       <c r="B51" t="str">
-        <v>ending</v>
+        <v>/oʊ/</v>
       </c>
       <c r="C51" t="str">
-        <v>结局</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D51" t="str">
-        <v>ending(结局)📢</v>
+        <v>欠</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>occasion</v>
       </c>
       <c r="B52" t="str">
-        <v>seal</v>
+        <v>/əˈkeɪʒn/</v>
       </c>
       <c r="C52" t="str">
-        <v>印章</v>
+        <v>n./vt.</v>
       </c>
       <c r="D52" t="str">
-        <v>seal(印章)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>intelligence</v>
-      </c>
-      <c r="C53" t="str">
-        <v>智力</v>
-      </c>
-      <c r="D53" t="str">
-        <v>intelligence(智力)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>cycle</v>
-      </c>
-      <c r="C54" t="str">
-        <v>循环</v>
-      </c>
-      <c r="D54" t="str">
-        <v>cycle(循环)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>cafeteria</v>
-      </c>
-      <c r="C55" t="str">
-        <v>自助餐厅</v>
-      </c>
-      <c r="D55" t="str">
-        <v>cafeteria(自助餐厅)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>troublesome</v>
-      </c>
-      <c r="C56" t="str">
-        <v>麻烦</v>
-      </c>
-      <c r="D56" t="str">
-        <v>troublesome(麻烦)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>reap</v>
-      </c>
-      <c r="C57" t="str">
-        <v>收获</v>
-      </c>
-      <c r="D57" t="str">
-        <v>reap(收获)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>light</v>
-      </c>
-      <c r="C58" t="str">
-        <v>光线</v>
-      </c>
-      <c r="D58" t="str">
-        <v>light(光线)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>owe</v>
-      </c>
-      <c r="C59" t="str">
-        <v>欠</v>
-      </c>
-      <c r="D59" t="str">
-        <v>owe(欠)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>occasion</v>
-      </c>
-      <c r="C60" t="str">
         <v>时机</v>
-      </c>
-      <c r="D60" t="str">
-        <v>occasion(时机)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>birth</v>
-      </c>
-      <c r="C61" t="str">
-        <v>出生</v>
-      </c>
-      <c r="D61" t="str">
-        <v>birth(出生)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
   </ignoredErrors>
 </worksheet>
 </file>